--- a/update-mapping-entete-page/ig/FRSectionPatientEducationLMCDAFHIR.xlsx
+++ b/update-mapping-entete-page/ig/FRSectionPatientEducationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T08:22:23+00:00</t>
+    <t>2026-08-14T10:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
